--- a/artfynd/A 4929-2025 artfynd.xlsx
+++ b/artfynd/A 4929-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404147</v>
       </c>
       <c r="B2" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404143</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137404144</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137404146</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137404145</v>
       </c>
       <c r="B6" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4929-2025 artfynd.xlsx
+++ b/artfynd/A 4929-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137404147</v>
       </c>
       <c r="B2" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137404143</v>
+        <v>137502429</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>96277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2387</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762853</v>
+        <v>763076</v>
       </c>
       <c r="R3" t="n">
-        <v>7294136</v>
+        <v>7294402</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,38 +898,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137404143</t>
+          <t>https://artportalen.se/Sighting/137502429</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137404144</v>
+        <v>137502426</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762862</v>
+        <v>763122</v>
       </c>
       <c r="R4" t="n">
-        <v>7294125</v>
+        <v>7294424</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,16 +1010,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137404144</t>
+          <t>https://artportalen.se/Sighting/137502426</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137404146</v>
+        <v>137404143</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762885</v>
+        <v>762853</v>
       </c>
       <c r="R5" t="n">
-        <v>7294091</v>
+        <v>7294136</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,16 +1122,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137404146</t>
+          <t>https://artportalen.se/Sighting/137404143</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137404145</v>
+        <v>137404144</v>
       </c>
       <c r="B6" t="n">
-        <v>79558</v>
+        <v>93489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>260591</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762865</v>
+        <v>762862</v>
       </c>
       <c r="R6" t="n">
-        <v>7294118</v>
+        <v>7294125</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gula apotecier</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,6 +1233,922 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404144</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137404146</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93489</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nymyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>762885</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7294091</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404146</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137502434</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80659</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nymyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>763079</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7294350</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137502434</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137502428</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nymyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>763079</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7294406</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137502428</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137502431</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nymyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>763077</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7294383</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137502431</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137502433</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nymyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>763083</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7294378</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137502433</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137502435</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nymyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>763066</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7294338</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137502435</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137502427</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nymyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>763097</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7294410</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137502427</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137404145</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79562</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nymyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>762865</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7294118</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gula apotecier</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137404145</t>
         </is>
@@ -1250,6 +2161,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
